--- a/src/test.demoApi/resources/testData/demoData.xlsx
+++ b/src/test.demoApi/resources/testData/demoData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fosman\IdeaProjects\mtf-dm-automation-test-api\src\test.demoApi\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rachowdhury\Documents\Software\mtf-dm-automation-test-api\src\test.demoApi\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3546B9-63D9-4988-8D7D-F48B3BF177C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34DBCB3-4274-449F-BFFA-35201F01256E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{3FAEF57A-74CB-4873-83C5-7175CED35448}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FAEF57A-74CB-4873-83C5-7175CED35448}"/>
   </bookViews>
   <sheets>
     <sheet name="Create" sheetId="1" r:id="rId1"/>
@@ -176,14 +176,14 @@
     <t>201</t>
   </si>
   <si>
-    <t>2024</t>
+    <t>2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +203,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -648,6 +654,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/test.demoApi/resources/testData/demoData.xlsx
+++ b/src/test.demoApi/resources/testData/demoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fosman\IdeaProjects\mtf-dm-automation-test-api\src\test.demoApi\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3546B9-63D9-4988-8D7D-F48B3BF177C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F147D8CE-F00E-422B-A2CB-470B991622B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{3FAEF57A-74CB-4873-83C5-7175CED35448}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{3FAEF57A-74CB-4873-83C5-7175CED35448}"/>
   </bookViews>
   <sheets>
     <sheet name="Create" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <t>201</t>
   </si>
   <si>
-    <t>2024</t>
+    <t>2025</t>
   </si>
 </sst>
 </file>

--- a/src/test.demoApi/resources/testData/demoData.xlsx
+++ b/src/test.demoApi/resources/testData/demoData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fosman\IdeaProjects\mtf-dm-automation-test-api\src\test.demoApi\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rachowdhury\Documents\Software\mtf-dm-automation-test-api\src\test.demoApi\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F147D8CE-F00E-422B-A2CB-470B991622B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34DBCB3-4274-449F-BFFA-35201F01256E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{3FAEF57A-74CB-4873-83C5-7175CED35448}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FAEF57A-74CB-4873-83C5-7175CED35448}"/>
   </bookViews>
   <sheets>
     <sheet name="Create" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +203,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -648,6 +654,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
